--- a/Dashboards/Data final/empleo_series.xlsx
+++ b/Dashboards/Data final/empleo_series.xlsx
@@ -381,7 +381,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>42.81845568746377</v>
+        <v>43.19946500861848</v>
       </c>
     </row>
     <row r="3">
@@ -394,7 +394,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>54.92867634439704</v>
+        <v>54.5276204409588</v>
       </c>
     </row>
     <row r="4">
@@ -420,7 +420,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>44.40936647134262</v>
+        <v>44.76819748375097</v>
       </c>
     </row>
     <row r="6">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>52.78038375270381</v>
+        <v>52.39884571129794</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>38.82025419437826</v>
+        <v>39.17685803826048</v>
       </c>
     </row>
     <row r="9">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>58.49355340236326</v>
+        <v>58.11227412664043</v>
       </c>
     </row>
     <row r="10">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>44.43810156568283</v>
+        <v>44.67555035695008</v>
       </c>
     </row>
     <row r="12">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>53.21383549645881</v>
+        <v>52.96384015871972</v>
       </c>
     </row>
     <row r="13">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>45.28735869703618</v>
+        <v>45.52861340384288</v>
       </c>
     </row>
     <row r="15">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>52.72446036992102</v>
+        <v>52.47261423049648</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>46.29894806082009</v>
+        <v>46.53187169487645</v>
       </c>
     </row>
     <row r="18">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>51.71099081331128</v>
+        <v>51.46805545568783</v>
       </c>
     </row>
     <row r="19">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>47.57195338854701</v>
+        <v>47.86404446319995</v>
       </c>
     </row>
     <row r="21">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>50.36685012799575</v>
+        <v>50.06210333809381</v>
       </c>
     </row>
     <row r="22">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>48.91312461089198</v>
+        <v>49.28423584154152</v>
       </c>
     </row>
     <row r="24">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>49.15457159002787</v>
+        <v>48.76879967992736</v>
       </c>
     </row>
     <row r="25">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>46.17194224985015</v>
+        <v>46.50281943043304</v>
       </c>
     </row>
     <row r="27">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>51.51392979535502</v>
+        <v>51.16646912064385</v>
       </c>
     </row>
     <row r="28">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>40.74096087322832</v>
+        <v>41.18860875336517</v>
       </c>
     </row>
     <row r="30">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>57.01862195621447</v>
+        <v>56.54635713098047</v>
       </c>
     </row>
     <row r="31">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>41.88428098021323</v>
+        <v>42.26429112816231</v>
       </c>
     </row>
     <row r="33">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>56.08518158591319</v>
+        <v>55.68674865947528</v>
       </c>
     </row>
     <row r="34">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>40.30517701938911</v>
+        <v>40.63761586806889</v>
       </c>
     </row>
     <row r="36">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>58.15113085440176</v>
+        <v>57.80595956609255</v>
       </c>
     </row>
     <row r="37">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>38.55788179605516</v>
+        <v>38.8482177152693</v>
       </c>
     </row>
     <row r="39">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>59.90180169329741</v>
+        <v>59.5998673877309</v>
       </c>
     </row>
     <row r="40">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>30.57369110975006</v>
+        <v>30.84822231465281</v>
       </c>
     </row>
     <row r="42">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>67.83065652039897</v>
+        <v>67.54179742927114</v>
       </c>
     </row>
     <row r="43">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>33.60712943950959</v>
+        <v>33.94123182907051</v>
       </c>
     </row>
     <row r="45">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>64.93908228941837</v>
+        <v>64.59052718868034</v>
       </c>
     </row>
     <row r="46">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>35.85299990056986</v>
+        <v>36.03571922987231</v>
       </c>
     </row>
     <row r="48">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C48">
-        <v>62.96410739649958</v>
+        <v>62.77535963549224</v>
       </c>
     </row>
     <row r="49">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C50">
-        <v>35.74721286783243</v>
+        <v>35.91641035696676</v>
       </c>
     </row>
     <row r="51">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C51">
-        <v>63.00103121944163</v>
+        <v>62.82590896190015</v>
       </c>
     </row>
     <row r="52">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>32.87280611429926</v>
+        <v>33.02956536674139</v>
       </c>
     </row>
     <row r="54">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>66.2190238964765</v>
+        <v>66.05793388966839</v>
       </c>
     </row>
     <row r="55">
